--- a/ujicoba.xlsx
+++ b/ujicoba.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\VelastoProductionSystem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66831821-2C12-4787-AB81-B8FE59359323}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7767F6A-9006-4262-AD6B-4B5023E1A4A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{149154D8-7F12-4866-802B-9D7CD381DF4A}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>NO</t>
   </si>
@@ -45,30 +45,9 @@
     <t>Part Name 1</t>
   </si>
   <si>
-    <t>Part Name 2</t>
-  </si>
-  <si>
-    <t>Compound</t>
-  </si>
-  <si>
-    <t>...</t>
-  </si>
-  <si>
     <t>Plan Target</t>
   </si>
   <si>
-    <t>(Dilewati)</t>
-  </si>
-  <si>
-    <t>Durasi</t>
-  </si>
-  <si>
-    <t>Waktu Mulai</t>
-  </si>
-  <si>
-    <t>Waktu Selesai</t>
-  </si>
-  <si>
     <t>RABU, 1 APRIL 2026 SHIFT 1</t>
   </si>
   <si>
@@ -78,26 +57,32 @@
     <t>HM0530</t>
   </si>
   <si>
-    <t>HM0531</t>
-  </si>
-  <si>
     <t>MS0120</t>
   </si>
   <si>
     <t>NA1610</t>
+  </si>
+  <si>
+    <t>NA1640</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
@@ -141,9 +126,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -458,22 +445,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EADB615-B2F9-4BC7-B8E7-2B692F730215}">
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -483,142 +463,72 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1">
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1">
         <v>1000</v>
       </c>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1">
+      <c r="B4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="1">
         <v>700</v>
       </c>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>1</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1">
+      <c r="B7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="1">
         <v>500</v>
       </c>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>2</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1">
+        <v>7</v>
+      </c>
+      <c r="C8" s="1">
         <v>1200</v>
       </c>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/ujicoba.xlsx
+++ b/ujicoba.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\VelastoProductionSystem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7767F6A-9006-4262-AD6B-4B5023E1A4A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99153B25-1EC1-44E1-816C-4F9F57E98013}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{149154D8-7F12-4866-802B-9D7CD381DF4A}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>NO</t>
   </si>
@@ -48,16 +48,7 @@
     <t>Plan Target</t>
   </si>
   <si>
-    <t>RABU, 1 APRIL 2026 SHIFT 1</t>
-  </si>
-  <si>
     <t>KAMIS, 2 APRIL 2026 SHIFT 1</t>
-  </si>
-  <si>
-    <t>HM0530</t>
-  </si>
-  <si>
-    <t>MS0120</t>
   </si>
   <si>
     <t>NA1610</t>
@@ -126,10 +117,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -445,7 +435,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EADB615-B2F9-4BC7-B8E7-2B692F730215}">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.5703125" bestFit="1" customWidth="1"/>
@@ -479,51 +469,17 @@
         <v>5</v>
       </c>
       <c r="C3" s="1">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>6</v>
+      <c r="B4" s="1" t="s">
+        <v>4</v>
       </c>
       <c r="C4" s="1">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="1"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>1</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="1">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>2</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="1">
         <v>1200</v>
       </c>
     </row>

--- a/ujicoba.xlsx
+++ b/ujicoba.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\VelastoProductionSystem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99153B25-1EC1-44E1-816C-4F9F57E98013}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{091155E9-0243-4E54-81E3-BC9FF019DAAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{149154D8-7F12-4866-802B-9D7CD381DF4A}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>NO</t>
   </si>
@@ -48,20 +48,38 @@
     <t>Plan Target</t>
   </si>
   <si>
-    <t>KAMIS, 2 APRIL 2026 SHIFT 1</t>
-  </si>
-  <si>
     <t>NA1610</t>
   </si>
   <si>
     <t>NA1640</t>
+  </si>
+  <si>
+    <t>KAMIS, 7 APRIL 2026 SHIFT 1</t>
+  </si>
+  <si>
+    <t>KAMIS, 8 APRIL 2026 SHIFT 2</t>
+  </si>
+  <si>
+    <t>KAMIS, 3 APRIL 2026 SHIFT 1</t>
+  </si>
+  <si>
+    <t>NA1270</t>
+  </si>
+  <si>
+    <t>NA1801</t>
+  </si>
+  <si>
+    <t>NA3312</t>
+  </si>
+  <si>
+    <t>TA0640</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -80,6 +98,11 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -117,10 +140,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -435,7 +459,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EADB615-B2F9-4BC7-B8E7-2B692F730215}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.5703125" bestFit="1" customWidth="1"/>
@@ -457,7 +481,7 @@
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C2" s="1"/>
     </row>
@@ -466,7 +490,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3" s="1">
         <v>500</v>
@@ -477,14 +501,73 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C4" s="1">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="1"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>1</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>2</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="1">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="1"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>1</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>2</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="1">
         <v>1200</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/ujicoba.xlsx
+++ b/ujicoba.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\VelastoProductionSystem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{091155E9-0243-4E54-81E3-BC9FF019DAAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05445C37-0404-4368-B3CD-0E6628B121C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{149154D8-7F12-4866-802B-9D7CD381DF4A}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>NO</t>
   </si>
@@ -54,15 +54,6 @@
     <t>NA1640</t>
   </si>
   <si>
-    <t>KAMIS, 7 APRIL 2026 SHIFT 1</t>
-  </si>
-  <si>
-    <t>KAMIS, 8 APRIL 2026 SHIFT 2</t>
-  </si>
-  <si>
-    <t>KAMIS, 3 APRIL 2026 SHIFT 1</t>
-  </si>
-  <si>
     <t>NA1270</t>
   </si>
   <si>
@@ -73,6 +64,18 @@
   </si>
   <si>
     <t>TA0640</t>
+  </si>
+  <si>
+    <t>RABU, 8 APRIL 2026 SHIFT 2</t>
+  </si>
+  <si>
+    <t>SELASA, 7 APRIL 2026 SHIFT 1</t>
+  </si>
+  <si>
+    <t>KAMIS, 9 APRIL 2026 SHIFT 1</t>
+  </si>
+  <si>
+    <t>SHIFT 1</t>
   </si>
 </sst>
 </file>
@@ -481,7 +484,7 @@
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1"/>
     </row>
@@ -510,16 +513,18 @@
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>1</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C6" s="1">
         <v>500</v>
@@ -530,7 +535,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C7" s="1">
         <v>1200</v>
@@ -539,7 +544,7 @@
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="1" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C8" s="1"/>
     </row>
@@ -548,7 +553,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C9" s="1">
         <v>500</v>
@@ -559,7 +564,7 @@
         <v>2</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C10" s="1">
         <v>1200</v>
